--- a/mining temp.xlsx
+++ b/mining temp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atultiwari\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atultiwari\Downloads\learning-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34FBA3F9-4C79-446F-B986-202CE5E13E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E39A8C-4CE3-45A0-9C8E-BCB6B69C97B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9CFE9C52-72CE-4474-9919-22D0859F696A}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="21" r:id="rId3"/>
+    <pivotCache cacheId="51" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -463,7 +463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -520,7 +520,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -535,24 +534,26 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="12">
     <dxf>
-      <alignment wrapText="1"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -562,120 +563,6 @@
     </dxf>
     <dxf>
       <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <alignment vertical="top"/>
@@ -697,26 +584,6 @@
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1334,7 +1201,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6546E12B-2665-4063-917B-8138AF0AC73D}" name="PivotTable2" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6546E12B-2665-4063-917B-8138AF0AC73D}" name="PivotTable2" cacheId="51" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:F19" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="12">
     <pivotField dataField="1" compact="0" outline="0" showAll="0">
@@ -1524,7 +1391,7 @@
     <dataField name="Sum of Offered Price" fld="8" baseField="11" baseItem="5"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="53">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -1533,7 +1400,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -1542,16 +1409,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="9">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="8">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="7">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -1561,16 +1428,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="5">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="4">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="3">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -1856,7 +1723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD30C3B-9F05-49BB-A682-ECDB108D6C37}">
-  <dimension ref="A3:G19"/>
+  <dimension ref="A3:G23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1872,23 +1739,23 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="27" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
+    <row r="4" spans="1:7" s="26" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="25" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1902,16 +1769,16 @@
       <c r="C5" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" s="23">
         <v>1120933.3999999999</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5">
         <v>2500000</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5">
         <v>3401322</v>
       </c>
     </row>
@@ -1919,13 +1786,13 @@
       <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" s="23">
         <v>1696362.15</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6">
         <v>4000000</v>
       </c>
     </row>
@@ -1936,13 +1803,13 @@
       <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7">
         <v>13</v>
       </c>
       <c r="E7" s="23">
         <v>38252995.491897002</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7">
         <v>41000000</v>
       </c>
     </row>
@@ -1953,13 +1820,13 @@
       <c r="C8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" s="23">
         <v>109422.28728345626</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8">
         <v>500000</v>
       </c>
     </row>
@@ -1967,13 +1834,13 @@
       <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" s="23">
         <v>2805566.2784952577</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9">
         <v>6000000</v>
       </c>
     </row>
@@ -1981,13 +1848,13 @@
       <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" s="23">
         <v>237377.2</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10">
         <v>1200000</v>
       </c>
     </row>
@@ -1995,13 +1862,13 @@
       <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" s="23">
         <v>471593.4</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11">
         <v>1600000</v>
       </c>
     </row>
@@ -2009,13 +1876,13 @@
       <c r="A12" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12">
         <v>22</v>
       </c>
       <c r="E12" s="23">
         <v>44694250.207675718</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12">
         <v>56800000</v>
       </c>
     </row>
@@ -2029,13 +1896,13 @@
       <c r="C13" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" s="23">
         <v>24105571.349682394</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13">
         <v>7000000</v>
       </c>
     </row>
@@ -2046,13 +1913,13 @@
       <c r="C14" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" s="23">
         <v>53641783.046680249</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14">
         <v>16000000</v>
       </c>
     </row>
@@ -2063,13 +1930,13 @@
       <c r="C15" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" s="23">
         <v>33616753.005078807</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15">
         <v>9400000</v>
       </c>
     </row>
@@ -2080,13 +1947,13 @@
       <c r="C16" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" s="23">
         <v>3885164.2111122236</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16">
         <v>0</v>
       </c>
     </row>
@@ -2097,13 +1964,13 @@
       <c r="C17" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17">
         <v>2</v>
       </c>
       <c r="E17" s="23">
         <v>426637.6738692674</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17">
         <v>800000</v>
       </c>
     </row>
@@ -2111,13 +1978,13 @@
       <c r="A18" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18">
         <v>12</v>
       </c>
       <c r="E18" s="23">
         <v>115675909.28642295</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18">
         <v>33200000</v>
       </c>
     </row>
@@ -2125,14 +1992,19 @@
       <c r="A19" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19">
         <v>34</v>
       </c>
       <c r="E19" s="23">
         <v>160370159.49409866</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19">
         <v>90000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2101,7 @@
         <v>2000000</v>
       </c>
       <c r="J2" s="13">
-        <f>I2-H2</f>
+        <f t="shared" ref="J2:J25" si="0">I2-H2</f>
         <v>1129837.1499999999</v>
       </c>
       <c r="K2" s="20" t="s">
@@ -2268,7 +2140,7 @@
         <v>2000000</v>
       </c>
       <c r="J3" s="13">
-        <f>I3-H3</f>
+        <f t="shared" si="0"/>
         <v>1101750.05</v>
       </c>
       <c r="K3" s="20" t="s">
@@ -2307,7 +2179,7 @@
         <v>2000000</v>
       </c>
       <c r="J4" s="13">
-        <f>I4-H4</f>
+        <f t="shared" si="0"/>
         <v>962846.52150474186</v>
       </c>
       <c r="K4" s="20" t="s">
@@ -2346,7 +2218,7 @@
         <v>1200000</v>
       </c>
       <c r="J5" s="13">
-        <f>I5-H5</f>
+        <f t="shared" si="0"/>
         <v>962622.8</v>
       </c>
       <c r="K5" s="20" t="s">
@@ -2385,7 +2257,7 @@
         <v>1600000</v>
       </c>
       <c r="J6" s="13">
-        <f>I6-H6</f>
+        <f t="shared" si="0"/>
         <v>1128406.6000000001</v>
       </c>
       <c r="K6" s="20" t="s">
@@ -2424,7 +2296,7 @@
         <v>2500000</v>
       </c>
       <c r="J7" s="13">
-        <f>I7-H7</f>
+        <f t="shared" si="0"/>
         <v>1643316.65</v>
       </c>
       <c r="K7" s="20" t="s">
@@ -2463,7 +2335,7 @@
         <v>2500000</v>
       </c>
       <c r="J8" s="13">
-        <f>I8-H8</f>
+        <f t="shared" si="0"/>
         <v>1643316.65</v>
       </c>
       <c r="K8" s="20" t="s">
@@ -2502,7 +2374,7 @@
         <v>2500000</v>
       </c>
       <c r="J9" s="13">
-        <f>I9-H9</f>
+        <f t="shared" si="0"/>
         <v>1643316.65</v>
       </c>
       <c r="K9" s="20" t="s">
@@ -2541,7 +2413,7 @@
         <v>3000000</v>
       </c>
       <c r="J10" s="13">
-        <f>I10-H10</f>
+        <f t="shared" si="0"/>
         <v>1459699.5636095891</v>
       </c>
       <c r="K10" s="20" t="s">
@@ -2580,7 +2452,7 @@
         <v>3000000</v>
       </c>
       <c r="J11" s="13">
-        <f>I11-H11</f>
+        <f t="shared" si="0"/>
         <v>1459699.5636095891</v>
       </c>
       <c r="K11" s="20" t="s">
@@ -2619,7 +2491,7 @@
         <v>3000000</v>
       </c>
       <c r="J12" s="13">
-        <f>I12-H12</f>
+        <f t="shared" si="0"/>
         <v>950963.48679163656</v>
       </c>
       <c r="K12" s="20" t="s">
@@ -2658,7 +2530,7 @@
         <v>2000000</v>
       </c>
       <c r="J13" s="13">
-        <f>I13-H13</f>
+        <f t="shared" si="0"/>
         <v>1167650.1000000001</v>
       </c>
       <c r="K13" s="20" t="s">
@@ -2697,7 +2569,7 @@
         <v>2000000</v>
       </c>
       <c r="J14" s="13">
-        <f>I14-H14</f>
+        <f t="shared" si="0"/>
         <v>1135987.75</v>
       </c>
       <c r="K14" s="20" t="s">
@@ -2736,7 +2608,7 @@
         <v>2500000</v>
       </c>
       <c r="J15" s="13">
-        <f>I15-H15</f>
+        <f t="shared" si="0"/>
         <v>1379066.6</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -2775,7 +2647,7 @@
         <v>500000</v>
       </c>
       <c r="J16" s="13">
-        <f>I16-H16</f>
+        <f t="shared" si="0"/>
         <v>390577.71271654376</v>
       </c>
       <c r="K16" s="20" t="s">
@@ -2814,7 +2686,7 @@
         <v>3500000</v>
       </c>
       <c r="J17" s="13">
-        <f>I17-H17</f>
+        <f t="shared" si="0"/>
         <v>-474078.81032328773</v>
       </c>
       <c r="K17" s="4" t="s">
@@ -2853,7 +2725,7 @@
         <v>3500000</v>
       </c>
       <c r="J18" s="13">
-        <f>I18-H18</f>
+        <f t="shared" si="0"/>
         <v>-474078.81032328773</v>
       </c>
       <c r="K18" s="4" t="s">
@@ -2892,7 +2764,7 @@
         <v>3500000</v>
       </c>
       <c r="J19" s="13">
-        <f>I19-H19</f>
+        <f t="shared" si="0"/>
         <v>-475271.16128219198</v>
       </c>
       <c r="K19" s="4" t="s">
@@ -2931,7 +2803,7 @@
         <v>3500000</v>
       </c>
       <c r="J20" s="13">
-        <f>I20-H20</f>
+        <f t="shared" si="0"/>
         <v>-1157469.8184947623</v>
       </c>
       <c r="K20" s="4" t="s">
@@ -2970,7 +2842,7 @@
         <v>3500000</v>
       </c>
       <c r="J21" s="13">
-        <f>I21-H21</f>
+        <f t="shared" si="0"/>
         <v>-1157469.8184947623</v>
       </c>
       <c r="K21" s="4" t="s">
@@ -3009,7 +2881,7 @@
         <v>3500000</v>
       </c>
       <c r="J22" s="13">
-        <f>I22-H22</f>
+        <f t="shared" si="0"/>
         <v>-1157469.8184947623</v>
       </c>
       <c r="K22" s="4" t="s">
@@ -3048,7 +2920,7 @@
         <v>3500000</v>
       </c>
       <c r="J23" s="13">
-        <f>I23-H23</f>
+        <f t="shared" si="0"/>
         <v>-1157469.8184947623</v>
       </c>
       <c r="K23" s="4" t="s">
@@ -3087,7 +2959,7 @@
         <v>400000</v>
       </c>
       <c r="J24" s="13">
-        <f>I24-H24</f>
+        <f t="shared" si="0"/>
         <v>135469.48289100657</v>
       </c>
       <c r="K24" s="21" t="s">
@@ -3126,7 +2998,7 @@
         <v>400000</v>
       </c>
       <c r="J25" s="13">
-        <f>I25-H25</f>
+        <f t="shared" si="0"/>
         <v>237892.84323972603</v>
       </c>
       <c r="K25" s="21" t="s">
@@ -3241,7 +3113,7 @@
         <v>2200000</v>
       </c>
       <c r="J28" s="13">
-        <f>I28-H28</f>
+        <f t="shared" ref="J28:J35" si="1">I28-H28</f>
         <v>-3254364.0278640483</v>
       </c>
       <c r="K28" s="4" t="s">
@@ -3280,7 +3152,7 @@
         <v>2200000</v>
       </c>
       <c r="J29" s="13">
-        <f>I29-H29</f>
+        <f t="shared" si="1"/>
         <v>-6165818.9869806161</v>
       </c>
       <c r="K29" s="4" t="s">
@@ -3319,7 +3191,7 @@
         <v>2500000</v>
       </c>
       <c r="J30" s="13">
-        <f>I30-H30</f>
+        <f t="shared" si="1"/>
         <v>-7243333.3108876701</v>
       </c>
       <c r="K30" s="4" t="s">
@@ -3358,7 +3230,7 @@
         <v>2500000</v>
       </c>
       <c r="J31" s="13">
-        <f>I31-H31</f>
+        <f t="shared" si="1"/>
         <v>-7553236.6793464758</v>
       </c>
       <c r="K31" s="4" t="s">
@@ -3397,7 +3269,7 @@
         <v>5000000</v>
       </c>
       <c r="J32" s="13">
-        <f>I32-H32</f>
+        <f t="shared" si="1"/>
         <v>-14231585.647913132</v>
       </c>
       <c r="K32" s="4" t="s">
@@ -3436,7 +3308,7 @@
         <v>5500000</v>
       </c>
       <c r="J33" s="13">
-        <f>I33-H33</f>
+        <f t="shared" si="1"/>
         <v>-12210498.694383562</v>
       </c>
       <c r="K33" s="4" t="s">
@@ -3475,7 +3347,7 @@
         <v>5500000</v>
       </c>
       <c r="J34" s="13">
-        <f>I34-H34</f>
+        <f t="shared" si="1"/>
         <v>-11199698.704383561</v>
       </c>
       <c r="K34" s="4" t="s">
@@ -3514,7 +3386,7 @@
         <v>7000000</v>
       </c>
       <c r="J35" s="13">
-        <f>I35-H35</f>
+        <f t="shared" si="1"/>
         <v>-17105571.349682394</v>
       </c>
       <c r="K35" s="4" t="s">
@@ -3526,12 +3398,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J1:J25 J28:J1048576">
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J25 J28:J1048576">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
